--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -838,13 +838,13 @@
     <t>0.7553,0.0004,0.0187,0.0649</t>
   </si>
   <si>
-    <t>0.5139,0.0002,0.0070,0.3639</t>
-  </si>
-  <si>
-    <t>0.6610,0.0004,0.0106,0.1788</t>
-  </si>
-  <si>
-    <t>0.8042,0.0004,0.0193,0.0568</t>
+    <t>0.5139,0.0002,0.0070,0.3640</t>
+  </si>
+  <si>
+    <t>0.6610,0.0004,0.0106,0.1789</t>
+  </si>
+  <si>
+    <t>0.8041,0.0004,0.0193,0.0568</t>
   </si>
   <si>
     <t>0.3819,0.0003,0.0020,0.8223</t>
@@ -925,7 +925,7 @@
     <t>0.6898,0.0007,0.0077,0.4008</t>
   </si>
   <si>
-    <t>0.7364,0.0023,0.0416,0.0929</t>
+    <t>0.7364,0.0023,0.0416,0.0930</t>
   </si>
   <si>
     <t>0.6693,0.0436,0.0906,0.0454</t>
@@ -1021,7 +1021,7 @@
     <t>0.0007,0.0068,0.9983,0.0004</t>
   </si>
   <si>
-    <t>0.2516,0.1089,0.1182,0.2578</t>
+    <t>0.2516,0.1089,0.1182,0.2579</t>
   </si>
   <si>
     <t>0.0008,0.9865,0.1452,0.0154</t>
@@ -1087,7 +1087,7 @@
     <t>0.5013,0.0002,0.0044,0.5350</t>
   </si>
   <si>
-    <t>0.3371,0.0008,0.0141,0.4964</t>
+    <t>0.3370,0.0008,0.0141,0.4965</t>
   </si>
   <si>
     <t>0.7582,0.0005,0.0045,0.3642</t>
@@ -1321,19 +1321,19 @@
     <t>0.7167,0.0004,0.0153,0.0956</t>
   </si>
   <si>
-    <t>0.7310,0.0004,0.0162,0.1019</t>
-  </si>
-  <si>
-    <t>0.6452,0.0005,0.0134,0.1690</t>
-  </si>
-  <si>
-    <t>0.5682,0.0005,0.0106,0.2776</t>
+    <t>0.7310,0.0004,0.0162,0.1020</t>
+  </si>
+  <si>
+    <t>0.6452,0.0005,0.0134,0.1691</t>
+  </si>
+  <si>
+    <t>0.5682,0.0005,0.0106,0.2777</t>
   </si>
   <si>
     <t>0.5923,0.0004,0.0145,0.1930</t>
   </si>
   <si>
-    <t>0.5871,0.0002,0.0067,0.3318</t>
+    <t>0.5871,0.0002,0.0067,0.3319</t>
   </si>
   <si>
     <t>0.4692,0.0049,0.0118,0.3993</t>
@@ -1348,7 +1348,7 @@
     <t>0.5055,0.0005,0.0088,0.4228</t>
   </si>
   <si>
-    <t>0.7171,0.0003,0.0038,0.3303</t>
+    <t>0.7170,0.0003,0.0038,0.3303</t>
   </si>
   <si>
     <t>0.4673,0.0016,0.0364,0.1666</t>
@@ -1372,7 +1372,7 @@
     <t>0.0167,0.0903,0.8649,0.0457</t>
   </si>
   <si>
-    <t>0.4403,0.0085,0.1294,0.1792</t>
+    <t>0.4403,0.0085,0.1294,0.1793</t>
   </si>
   <si>
     <t>0.0090,0.1764,0.9653,0.0029</t>
@@ -1420,7 +1420,7 @@
     <t>0.7080,0.0015,0.0212,0.0986</t>
   </si>
   <si>
-    <t>0.6509,0.0011,0.0105,0.2803</t>
+    <t>0.6509,0.0011,0.0105,0.2804</t>
   </si>
   <si>
     <t>0.4972,0.0010,0.0075,0.4582</t>
@@ -1471,7 +1471,7 @@
     <t>0.5670,0.0004,0.0091,0.2916</t>
   </si>
   <si>
-    <t>0.6168,0.0005,0.0127,0.1972</t>
+    <t>0.6168,0.0005,0.0127,0.1973</t>
   </si>
   <si>
     <t>0.5112,0.0007,0.0204,0.2336</t>
@@ -1531,10 +1531,10 @@
     <t>0.6636,0.0005,0.0143,0.1463</t>
   </si>
   <si>
-    <t>0.4376,0.0019,0.0301,0.2302</t>
-  </si>
-  <si>
-    <t>0.6486,0.0007,0.0093,0.3331</t>
+    <t>0.4375,0.0019,0.0301,0.2303</t>
+  </si>
+  <si>
+    <t>0.6486,0.0007,0.0093,0.3332</t>
   </si>
   <si>
     <t>0.5204,0.0010,0.0141,0.3105</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="526">
   <si>
     <t>Filename</t>
   </si>
@@ -814,6 +814,12 @@
     <t>0,0,0,1</t>
   </si>
   <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,0</t>
   </si>
   <si>
@@ -823,76 +829,76 @@
     <t>0,1,0,0</t>
   </si>
   <si>
-    <t>0.8264,0.0010,0.0100,0.1864</t>
+    <t>0.8266,0.0010,0.0100,0.1862</t>
   </si>
   <si>
     <t>0.3014,0.0002,0.0010,0.9094</t>
   </si>
   <si>
-    <t>0.5800,0.0001,0.0013,0.6665</t>
-  </si>
-  <si>
-    <t>0.5845,0.0004,0.0036,0.6272</t>
-  </si>
-  <si>
-    <t>0.7553,0.0004,0.0187,0.0649</t>
-  </si>
-  <si>
-    <t>0.5139,0.0002,0.0070,0.3640</t>
-  </si>
-  <si>
-    <t>0.6610,0.0004,0.0106,0.1789</t>
-  </si>
-  <si>
-    <t>0.8041,0.0004,0.0193,0.0568</t>
-  </si>
-  <si>
-    <t>0.3819,0.0003,0.0020,0.8223</t>
-  </si>
-  <si>
-    <t>0.4375,0.0003,0.0061,0.5151</t>
-  </si>
-  <si>
-    <t>0.5945,0.0002,0.0064,0.3334</t>
-  </si>
-  <si>
-    <t>0.6636,0.0002,0.0115,0.1481</t>
-  </si>
-  <si>
-    <t>0.8646,0.0009,0.0179,0.0544</t>
-  </si>
-  <si>
-    <t>0.4778,0.0157,0.3521,0.0163</t>
+    <t>0.5800,0.0001,0.0013,0.6664</t>
+  </si>
+  <si>
+    <t>0.5843,0.0004,0.0036,0.6272</t>
+  </si>
+  <si>
+    <t>0.7551,0.0004,0.0187,0.0650</t>
+  </si>
+  <si>
+    <t>0.5137,0.0002,0.0071,0.3640</t>
+  </si>
+  <si>
+    <t>0.6608,0.0004,0.0106,0.1787</t>
+  </si>
+  <si>
+    <t>0.8039,0.0004,0.0193,0.0568</t>
+  </si>
+  <si>
+    <t>0.3820,0.0003,0.0020,0.8222</t>
+  </si>
+  <si>
+    <t>0.4374,0.0003,0.0061,0.5151</t>
+  </si>
+  <si>
+    <t>0.5940,0.0002,0.0064,0.3336</t>
+  </si>
+  <si>
+    <t>0.6633,0.0002,0.0115,0.1481</t>
+  </si>
+  <si>
+    <t>0.8646,0.0009,0.0179,0.0543</t>
+  </si>
+  <si>
+    <t>0.4778,0.0157,0.3523,0.0162</t>
   </si>
   <si>
     <t>0.8756,0.0025,0.1161,0.0039</t>
   </si>
   <si>
-    <t>0.5357,0.0149,0.4198,0.0057</t>
+    <t>0.5357,0.0149,0.4199,0.0057</t>
   </si>
   <si>
     <t>0.8683,0.0013,0.0343,0.0255</t>
   </si>
   <si>
-    <t>0.4009,0.0891,0.1335,0.0599</t>
-  </si>
-  <si>
-    <t>0.5507,0.0121,0.0342,0.1489</t>
-  </si>
-  <si>
-    <t>0.2614,0.0164,0.0111,0.6030</t>
-  </si>
-  <si>
-    <t>0.5371,0.0100,0.0602,0.0957</t>
-  </si>
-  <si>
-    <t>0.2228,0.4887,0.2999,0.0264</t>
+    <t>0.4011,0.0890,0.1336,0.0598</t>
+  </si>
+  <si>
+    <t>0.5509,0.0121,0.0342,0.1488</t>
+  </si>
+  <si>
+    <t>0.2616,0.0164,0.0111,0.6028</t>
+  </si>
+  <si>
+    <t>0.5371,0.0100,0.0603,0.0957</t>
+  </si>
+  <si>
+    <t>0.2231,0.4883,0.3000,0.0264</t>
   </si>
   <si>
     <t>0.8660,0.0008,0.0127,0.0775</t>
   </si>
   <si>
-    <t>0.6307,0.0095,0.0985,0.0958</t>
+    <t>0.6309,0.0095,0.0986,0.0957</t>
   </si>
   <si>
     <t>0.4522,0.0038,0.4899,0.0069</t>
@@ -901,10 +907,10 @@
     <t>0.6198,0.0056,0.2630,0.0165</t>
   </si>
   <si>
-    <t>0.7361,0.0023,0.0713,0.0508</t>
-  </si>
-  <si>
-    <t>0.6361,0.0036,0.3636,0.0045</t>
+    <t>0.7358,0.0023,0.0715,0.0508</t>
+  </si>
+  <si>
+    <t>0.6362,0.0036,0.3636,0.0045</t>
   </si>
   <si>
     <t>0.0964,0.0042,0.9236,0.0012</t>
@@ -913,106 +919,106 @@
     <t>0.8802,0.0016,0.0140,0.0678</t>
   </si>
   <si>
-    <t>0.5558,0.0005,0.0026,0.6826</t>
-  </si>
-  <si>
-    <t>0.0460,0.0111,0.8893,0.0165</t>
-  </si>
-  <si>
-    <t>0.5481,0.0126,0.3051,0.0185</t>
-  </si>
-  <si>
-    <t>0.6898,0.0007,0.0077,0.4008</t>
-  </si>
-  <si>
-    <t>0.7364,0.0023,0.0416,0.0930</t>
-  </si>
-  <si>
-    <t>0.6693,0.0436,0.0906,0.0454</t>
-  </si>
-  <si>
-    <t>0.2520,0.0676,0.1995,0.2126</t>
-  </si>
-  <si>
-    <t>0.0037,0.7783,0.9302,0.0010</t>
-  </si>
-  <si>
-    <t>0.0145,0.0441,0.9716,0.0019</t>
-  </si>
-  <si>
-    <t>0.1399,0.0342,0.7909,0.0040</t>
+    <t>0.5559,0.0005,0.0026,0.6825</t>
+  </si>
+  <si>
+    <t>0.0459,0.0111,0.8894,0.0165</t>
+  </si>
+  <si>
+    <t>0.5481,0.0125,0.3051,0.0185</t>
+  </si>
+  <si>
+    <t>0.6896,0.0007,0.0077,0.4009</t>
+  </si>
+  <si>
+    <t>0.7362,0.0023,0.0417,0.0929</t>
+  </si>
+  <si>
+    <t>0.6695,0.0436,0.0907,0.0454</t>
+  </si>
+  <si>
+    <t>0.2519,0.0676,0.1998,0.2124</t>
+  </si>
+  <si>
+    <t>0.0037,0.7781,0.9302,0.0010</t>
+  </si>
+  <si>
+    <t>0.0146,0.0441,0.9716,0.0019</t>
+  </si>
+  <si>
+    <t>0.1400,0.0342,0.7909,0.0040</t>
   </si>
   <si>
     <t>0.8034,0.0032,0.0517,0.1392</t>
   </si>
   <si>
-    <t>0.0366,0.2536,0.8893,0.0097</t>
-  </si>
-  <si>
-    <t>0.0018,0.9848,0.3252,0.0024</t>
-  </si>
-  <si>
-    <t>0.0290,0.0330,0.9514,0.0039</t>
-  </si>
-  <si>
-    <t>0.2123,0.0011,0.0017,0.8811</t>
-  </si>
-  <si>
-    <t>0.0038,0.9013,0.0722,0.1724</t>
-  </si>
-  <si>
-    <t>0.0014,0.9761,0.3253,0.0220</t>
-  </si>
-  <si>
-    <t>0.0010,0.9835,0.2874,0.0190</t>
-  </si>
-  <si>
-    <t>0.0009,0.0560,0.9956,0.0004</t>
-  </si>
-  <si>
-    <t>0.0388,0.1947,0.8832,0.0088</t>
-  </si>
-  <si>
-    <t>0.1958,0.0152,0.7661,0.0084</t>
-  </si>
-  <si>
-    <t>0.6133,0.0033,0.3213,0.0063</t>
-  </si>
-  <si>
-    <t>0.1785,0.0175,0.7982,0.0041</t>
-  </si>
-  <si>
-    <t>0.3610,0.0135,0.5854,0.0102</t>
-  </si>
-  <si>
-    <t>0.5812,0.0008,0.0097,0.3013</t>
-  </si>
-  <si>
-    <t>0.6403,0.0004,0.0110,0.2110</t>
-  </si>
-  <si>
-    <t>0.6624,0.0009,0.0260,0.1100</t>
-  </si>
-  <si>
-    <t>0.2767,0.0028,0.1306,0.1232</t>
-  </si>
-  <si>
-    <t>0.6221,0.0004,0.0109,0.2376</t>
-  </si>
-  <si>
-    <t>0.6582,0.0001,0.0040,0.2946</t>
-  </si>
-  <si>
-    <t>0.7503,0.0006,0.0169,0.0997</t>
-  </si>
-  <si>
-    <t>0.0006,0.9895,0.8201,0.0003</t>
-  </si>
-  <si>
-    <t>0.0026,0.1413,0.9908,0.0004</t>
-  </si>
-  <si>
-    <t>0.0071,0.0795,0.9813,0.0010</t>
+    <t>0.0366,0.2533,0.8894,0.0097</t>
+  </si>
+  <si>
+    <t>0.0018,0.9847,0.3255,0.0024</t>
+  </si>
+  <si>
+    <t>0.0290,0.0329,0.9514,0.0038</t>
+  </si>
+  <si>
+    <t>0.2123,0.0011,0.0017,0.8812</t>
+  </si>
+  <si>
+    <t>0.0038,0.9012,0.0723,0.1724</t>
+  </si>
+  <si>
+    <t>0.0014,0.9761,0.3255,0.0220</t>
+  </si>
+  <si>
+    <t>0.0010,0.9835,0.2877,0.0190</t>
+  </si>
+  <si>
+    <t>0.0009,0.0559,0.9956,0.0004</t>
+  </si>
+  <si>
+    <t>0.0388,0.1945,0.8832,0.0088</t>
+  </si>
+  <si>
+    <t>0.1958,0.0152,0.7662,0.0084</t>
+  </si>
+  <si>
+    <t>0.6132,0.0033,0.3213,0.0063</t>
+  </si>
+  <si>
+    <t>0.1785,0.0175,0.7983,0.0041</t>
+  </si>
+  <si>
+    <t>0.3611,0.0135,0.5854,0.0102</t>
+  </si>
+  <si>
+    <t>0.5810,0.0008,0.0097,0.3012</t>
+  </si>
+  <si>
+    <t>0.6400,0.0004,0.0110,0.2110</t>
+  </si>
+  <si>
+    <t>0.6623,0.0009,0.0261,0.1100</t>
+  </si>
+  <si>
+    <t>0.2766,0.0027,0.1307,0.1232</t>
+  </si>
+  <si>
+    <t>0.6218,0.0004,0.0109,0.2377</t>
+  </si>
+  <si>
+    <t>0.6581,0.0001,0.0040,0.2945</t>
+  </si>
+  <si>
+    <t>0.7502,0.0006,0.0169,0.0997</t>
+  </si>
+  <si>
+    <t>0.0006,0.9895,0.8203,0.0003</t>
+  </si>
+  <si>
+    <t>0.0026,0.1411,0.9908,0.0004</t>
+  </si>
+  <si>
+    <t>0.0071,0.0793,0.9813,0.0010</t>
   </si>
   <si>
     <t>0.0010,0.9456,0.9115,0.0005</t>
@@ -1021,31 +1027,31 @@
     <t>0.0007,0.0068,0.9983,0.0004</t>
   </si>
   <si>
-    <t>0.2516,0.1089,0.1182,0.2579</t>
-  </si>
-  <si>
-    <t>0.0008,0.9865,0.1452,0.0154</t>
+    <t>0.2518,0.1088,0.1182,0.2578</t>
+  </si>
+  <si>
+    <t>0.0008,0.9865,0.1454,0.0154</t>
   </si>
   <si>
     <t>0.9397,0.0009,0.0131,0.0230</t>
   </si>
   <si>
-    <t>0.4792,0.0408,0.2964,0.0437</t>
-  </si>
-  <si>
-    <t>0.2258,0.0237,0.6268,0.0147</t>
-  </si>
-  <si>
-    <t>0.0022,0.8199,0.9420,0.0006</t>
-  </si>
-  <si>
-    <t>0.0038,0.6879,0.9531,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.9934,0.7461,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.8558,0.9228,0.0010</t>
+    <t>0.4791,0.0408,0.2967,0.0436</t>
+  </si>
+  <si>
+    <t>0.2258,0.0237,0.6270,0.0147</t>
+  </si>
+  <si>
+    <t>0.0022,0.8197,0.9421,0.0006</t>
+  </si>
+  <si>
+    <t>0.0038,0.6875,0.9532,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.9934,0.7463,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.8557,0.9228,0.0010</t>
   </si>
   <si>
     <t>0.1698,0.0001,0.0008,0.9566</t>
@@ -1057,223 +1063,223 @@
     <t>0.2117,0.0001,0.0004,0.9566</t>
   </si>
   <si>
-    <t>0.0778,0.0000,0.0003,0.9894</t>
-  </si>
-  <si>
-    <t>0.1106,0.0002,0.0008,0.9731</t>
+    <t>0.0777,0.0000,0.0003,0.9894</t>
+  </si>
+  <si>
+    <t>0.1107,0.0002,0.0008,0.9731</t>
   </si>
   <si>
     <t>0.0309,0.0002,0.0007,0.9953</t>
   </si>
   <si>
-    <t>0.0024,0.9425,0.8898,0.0005</t>
-  </si>
-  <si>
-    <t>0.0026,0.6988,0.9588,0.0006</t>
-  </si>
-  <si>
-    <t>0.0141,0.4270,0.9144,0.0021</t>
-  </si>
-  <si>
-    <t>0.0165,0.2380,0.9493,0.0014</t>
-  </si>
-  <si>
-    <t>0.0005,0.9716,0.9237,0.0002</t>
-  </si>
-  <si>
-    <t>0.0080,0.8715,0.8405,0.0021</t>
-  </si>
-  <si>
-    <t>0.5013,0.0002,0.0044,0.5350</t>
-  </si>
-  <si>
-    <t>0.3370,0.0008,0.0141,0.4965</t>
-  </si>
-  <si>
-    <t>0.7582,0.0005,0.0045,0.3642</t>
-  </si>
-  <si>
-    <t>0.4207,0.0004,0.0030,0.6901</t>
-  </si>
-  <si>
-    <t>0.6466,0.0008,0.0069,0.3210</t>
-  </si>
-  <si>
-    <t>0.7355,0.0019,0.0255,0.1470</t>
-  </si>
-  <si>
-    <t>0.4290,0.0009,0.0119,0.4380</t>
+    <t>0.0024,0.9425,0.8899,0.0005</t>
+  </si>
+  <si>
+    <t>0.0026,0.6985,0.9589,0.0006</t>
+  </si>
+  <si>
+    <t>0.0141,0.4266,0.9144,0.0021</t>
+  </si>
+  <si>
+    <t>0.0165,0.2377,0.9494,0.0014</t>
+  </si>
+  <si>
+    <t>0.0005,0.9716,0.9238,0.0002</t>
+  </si>
+  <si>
+    <t>0.0080,0.8713,0.8406,0.0021</t>
+  </si>
+  <si>
+    <t>0.5013,0.0002,0.0044,0.5349</t>
+  </si>
+  <si>
+    <t>0.3369,0.0008,0.0141,0.4963</t>
+  </si>
+  <si>
+    <t>0.7582,0.0005,0.0045,0.3640</t>
+  </si>
+  <si>
+    <t>0.4205,0.0004,0.0030,0.6901</t>
+  </si>
+  <si>
+    <t>0.6465,0.0008,0.0069,0.3210</t>
+  </si>
+  <si>
+    <t>0.7355,0.0019,0.0255,0.1469</t>
+  </si>
+  <si>
+    <t>0.4289,0.0009,0.0119,0.4379</t>
   </si>
   <si>
     <t>0.8307,0.0088,0.0474,0.0228</t>
   </si>
   <si>
-    <t>0.5839,0.0002,0.0116,0.1929</t>
-  </si>
-  <si>
-    <t>0.7258,0.0003,0.0071,0.2461</t>
-  </si>
-  <si>
-    <t>0.6005,0.0001,0.0033,0.4057</t>
-  </si>
-  <si>
-    <t>0.7522,0.0002,0.0034,0.2876</t>
-  </si>
-  <si>
-    <t>0.3826,0.0003,0.0058,0.6510</t>
-  </si>
-  <si>
-    <t>0.8978,0.0018,0.0193,0.0529</t>
-  </si>
-  <si>
-    <t>0.6358,0.0001,0.0018,0.5248</t>
-  </si>
-  <si>
-    <t>0.7667,0.0003,0.0085,0.1305</t>
+    <t>0.5837,0.0002,0.0116,0.1929</t>
+  </si>
+  <si>
+    <t>0.7256,0.0003,0.0071,0.2460</t>
+  </si>
+  <si>
+    <t>0.6003,0.0001,0.0033,0.4057</t>
+  </si>
+  <si>
+    <t>0.7521,0.0002,0.0034,0.2876</t>
+  </si>
+  <si>
+    <t>0.3825,0.0003,0.0058,0.6510</t>
+  </si>
+  <si>
+    <t>0.8978,0.0018,0.0193,0.0528</t>
+  </si>
+  <si>
+    <t>0.6357,0.0001,0.0018,0.5246</t>
+  </si>
+  <si>
+    <t>0.7665,0.0003,0.0085,0.1305</t>
   </si>
   <si>
     <t>0.0623,0.0049,0.9466,0.0014</t>
   </si>
   <si>
-    <t>0.4980,0.0078,0.3236,0.0241</t>
+    <t>0.4979,0.0077,0.3237,0.0241</t>
   </si>
   <si>
     <t>0.9575,0.0003,0.0071,0.0150</t>
   </si>
   <si>
-    <t>0.6367,0.0061,0.2321,0.0199</t>
-  </si>
-  <si>
-    <t>0.1892,0.0620,0.0580,0.3344</t>
-  </si>
-  <si>
-    <t>0.1863,0.2631,0.1267,0.0652</t>
-  </si>
-  <si>
-    <t>0.3183,0.0453,0.0353,0.2289</t>
-  </si>
-  <si>
-    <t>0.5115,0.0270,0.1027,0.0461</t>
-  </si>
-  <si>
-    <t>0.1744,0.2401,0.1612,0.0971</t>
-  </si>
-  <si>
-    <t>0.0876,0.3999,0.0902,0.0710</t>
-  </si>
-  <si>
-    <t>0.7496,0.0056,0.0335,0.0639</t>
+    <t>0.6367,0.0061,0.2322,0.0199</t>
+  </si>
+  <si>
+    <t>0.1892,0.0620,0.0580,0.3345</t>
+  </si>
+  <si>
+    <t>0.1864,0.2628,0.1267,0.0652</t>
+  </si>
+  <si>
+    <t>0.3186,0.0452,0.0354,0.2288</t>
+  </si>
+  <si>
+    <t>0.5116,0.0270,0.1028,0.0460</t>
+  </si>
+  <si>
+    <t>0.1745,0.2397,0.1612,0.0971</t>
+  </si>
+  <si>
+    <t>0.0877,0.3995,0.0902,0.0710</t>
+  </si>
+  <si>
+    <t>0.7497,0.0056,0.0335,0.0638</t>
   </si>
   <si>
     <t>0.6813,0.0078,0.0572,0.0948</t>
   </si>
   <si>
-    <t>0.7155,0.0099,0.2205,0.0146</t>
-  </si>
-  <si>
-    <t>0.7145,0.0110,0.1065,0.0422</t>
+    <t>0.7157,0.0099,0.2205,0.0146</t>
+  </si>
+  <si>
+    <t>0.7146,0.0110,0.1065,0.0421</t>
   </si>
   <si>
     <t>0.7162,0.0059,0.0644,0.0653</t>
   </si>
   <si>
-    <t>0.0483,0.1288,0.2722,0.5677</t>
-  </si>
-  <si>
-    <t>0.0008,0.9748,0.1549,0.0788</t>
-  </si>
-  <si>
-    <t>0.0009,0.9718,0.1673,0.0808</t>
-  </si>
-  <si>
-    <t>0.2563,0.0760,0.0569,0.2334</t>
-  </si>
-  <si>
-    <t>0.0003,0.9884,0.3720,0.0071</t>
-  </si>
-  <si>
-    <t>0.1418,0.2880,0.5245,0.0500</t>
-  </si>
-  <si>
-    <t>0.4894,0.0203,0.1065,0.0722</t>
-  </si>
-  <si>
-    <t>0.6096,0.0150,0.0875,0.0490</t>
-  </si>
-  <si>
-    <t>0.4020,0.0001,0.0037,0.7255</t>
-  </si>
-  <si>
-    <t>0.8498,0.0002,0.0023,0.2257</t>
-  </si>
-  <si>
-    <t>0.5513,0.0002,0.0028,0.5441</t>
-  </si>
-  <si>
-    <t>0.7670,0.0005,0.0132,0.0993</t>
-  </si>
-  <si>
-    <t>0.8036,0.0013,0.0145,0.1898</t>
-  </si>
-  <si>
-    <t>0.4808,0.0002,0.0075,0.4943</t>
-  </si>
-  <si>
-    <t>0.6611,0.0002,0.0041,0.3225</t>
-  </si>
-  <si>
-    <t>0.7763,0.0003,0.0105,0.0909</t>
-  </si>
-  <si>
-    <t>0.0470,0.2605,0.8380,0.0097</t>
-  </si>
-  <si>
-    <t>0.0034,0.6493,0.9607,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.4091,0.9878,0.0004</t>
-  </si>
-  <si>
-    <t>0.1951,0.0273,0.7494,0.0030</t>
+    <t>0.0483,0.1287,0.2722,0.5677</t>
+  </si>
+  <si>
+    <t>0.0008,0.9748,0.1550,0.0788</t>
+  </si>
+  <si>
+    <t>0.0009,0.9718,0.1676,0.0808</t>
+  </si>
+  <si>
+    <t>0.2565,0.0758,0.0569,0.2333</t>
+  </si>
+  <si>
+    <t>0.0003,0.9884,0.3723,0.0071</t>
+  </si>
+  <si>
+    <t>0.1418,0.2878,0.5247,0.0499</t>
+  </si>
+  <si>
+    <t>0.4896,0.0203,0.1065,0.0721</t>
+  </si>
+  <si>
+    <t>0.6097,0.0150,0.0875,0.0490</t>
+  </si>
+  <si>
+    <t>0.4020,0.0001,0.0037,0.7252</t>
+  </si>
+  <si>
+    <t>0.8498,0.0002,0.0023,0.2256</t>
+  </si>
+  <si>
+    <t>0.5512,0.0002,0.0028,0.5440</t>
+  </si>
+  <si>
+    <t>0.7670,0.0005,0.0132,0.0992</t>
+  </si>
+  <si>
+    <t>0.8034,0.0013,0.0145,0.1896</t>
+  </si>
+  <si>
+    <t>0.4807,0.0002,0.0075,0.4941</t>
+  </si>
+  <si>
+    <t>0.6609,0.0002,0.0041,0.3226</t>
+  </si>
+  <si>
+    <t>0.7762,0.0003,0.0105,0.0909</t>
+  </si>
+  <si>
+    <t>0.0470,0.2602,0.8381,0.0097</t>
+  </si>
+  <si>
+    <t>0.0034,0.6490,0.9607,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.4087,0.9878,0.0004</t>
+  </si>
+  <si>
+    <t>0.1952,0.0272,0.7494,0.0030</t>
   </si>
   <si>
     <t>0.9340,0.0003,0.0052,0.0427</t>
   </si>
   <si>
-    <t>0.7616,0.0054,0.0323,0.1058</t>
-  </si>
-  <si>
-    <t>0.7186,0.0045,0.2257,0.0127</t>
-  </si>
-  <si>
-    <t>0.7027,0.0088,0.1572,0.0233</t>
-  </si>
-  <si>
-    <t>0.2320,0.0000,0.0003,0.9532</t>
+    <t>0.7617,0.0054,0.0323,0.1058</t>
+  </si>
+  <si>
+    <t>0.7187,0.0045,0.2258,0.0127</t>
+  </si>
+  <si>
+    <t>0.7027,0.0088,0.1574,0.0233</t>
+  </si>
+  <si>
+    <t>0.2319,0.0000,0.0003,0.9532</t>
   </si>
   <si>
     <t>0.0078,0.0003,0.0005,0.9988</t>
   </si>
   <si>
-    <t>0.0759,0.0002,0.0005,0.9852</t>
+    <t>0.0758,0.0002,0.0005,0.9852</t>
   </si>
   <si>
     <t>0.0651,0.0001,0.0007,0.9887</t>
   </si>
   <si>
-    <t>0.0010,0.9786,0.7997,0.0009</t>
-  </si>
-  <si>
-    <t>0.6750,0.0003,0.0049,0.3383</t>
-  </si>
-  <si>
-    <t>0.4383,0.0035,0.0222,0.3335</t>
-  </si>
-  <si>
-    <t>0.8031,0.0006,0.0113,0.0975</t>
-  </si>
-  <si>
-    <t>0.6030,0.0027,0.0315,0.1256</t>
+    <t>0.0010,0.9786,0.7998,0.0009</t>
+  </si>
+  <si>
+    <t>0.6749,0.0003,0.0049,0.3383</t>
+  </si>
+  <si>
+    <t>0.4382,0.0035,0.0223,0.3333</t>
+  </si>
+  <si>
+    <t>0.8029,0.0006,0.0113,0.0975</t>
+  </si>
+  <si>
+    <t>0.6028,0.0027,0.0315,0.1256</t>
   </si>
   <si>
     <t>0.8515,0.0003,0.0050,0.1358</t>
@@ -1282,211 +1288,211 @@
     <t>0.0070,0.0000,0.9979,0.0000</t>
   </si>
   <si>
-    <t>0.0506,0.0000,0.9784,0.0000</t>
+    <t>0.0505,0.0000,0.9785,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0025</t>
   </si>
   <si>
-    <t>0.8349,0.0018,0.1097,0.0116</t>
-  </si>
-  <si>
-    <t>0.7977,0.0029,0.0410,0.0753</t>
-  </si>
-  <si>
-    <t>0.4887,0.0041,0.0401,0.3168</t>
-  </si>
-  <si>
-    <t>0.8235,0.0004,0.0036,0.1976</t>
-  </si>
-  <si>
-    <t>0.8843,0.0017,0.0136,0.0730</t>
-  </si>
-  <si>
-    <t>0.4463,0.0053,0.0154,0.4234</t>
-  </si>
-  <si>
-    <t>0.8167,0.0012,0.0196,0.0848</t>
+    <t>0.8348,0.0018,0.1098,0.0116</t>
+  </si>
+  <si>
+    <t>0.7976,0.0029,0.0411,0.0752</t>
+  </si>
+  <si>
+    <t>0.4885,0.0041,0.0402,0.3169</t>
+  </si>
+  <si>
+    <t>0.8234,0.0004,0.0036,0.1976</t>
+  </si>
+  <si>
+    <t>0.8843,0.0016,0.0136,0.0730</t>
+  </si>
+  <si>
+    <t>0.4465,0.0053,0.0154,0.4232</t>
+  </si>
+  <si>
+    <t>0.8166,0.0012,0.0196,0.0848</t>
   </si>
   <si>
     <t>0.8022,0.0122,0.0775,0.0502</t>
   </si>
   <si>
-    <t>0.5799,0.0003,0.0087,0.2914</t>
-  </si>
-  <si>
-    <t>0.4418,0.0002,0.0026,0.7871</t>
-  </si>
-  <si>
-    <t>0.7167,0.0004,0.0153,0.0956</t>
-  </si>
-  <si>
-    <t>0.7310,0.0004,0.0162,0.1020</t>
-  </si>
-  <si>
-    <t>0.6452,0.0005,0.0134,0.1691</t>
-  </si>
-  <si>
-    <t>0.5682,0.0005,0.0106,0.2777</t>
-  </si>
-  <si>
-    <t>0.5923,0.0004,0.0145,0.1930</t>
-  </si>
-  <si>
-    <t>0.5871,0.0002,0.0067,0.3319</t>
-  </si>
-  <si>
-    <t>0.4692,0.0049,0.0118,0.3993</t>
-  </si>
-  <si>
-    <t>0.6021,0.0139,0.1180,0.0329</t>
-  </si>
-  <si>
-    <t>0.7589,0.0063,0.0417,0.0677</t>
-  </si>
-  <si>
-    <t>0.5055,0.0005,0.0088,0.4228</t>
-  </si>
-  <si>
-    <t>0.7170,0.0003,0.0038,0.3303</t>
-  </si>
-  <si>
-    <t>0.4673,0.0016,0.0364,0.1666</t>
-  </si>
-  <si>
-    <t>0.7737,0.0007,0.0101,0.1509</t>
-  </si>
-  <si>
-    <t>0.6009,0.0007,0.0093,0.2669</t>
-  </si>
-  <si>
-    <t>0.1759,0.0115,0.6570,0.0098</t>
-  </si>
-  <si>
-    <t>0.5664,0.0020,0.0526,0.0750</t>
+    <t>0.5797,0.0003,0.0087,0.2913</t>
+  </si>
+  <si>
+    <t>0.4418,0.0002,0.0026,0.7870</t>
+  </si>
+  <si>
+    <t>0.7166,0.0004,0.0154,0.0956</t>
+  </si>
+  <si>
+    <t>0.7308,0.0004,0.0162,0.1020</t>
+  </si>
+  <si>
+    <t>0.6450,0.0005,0.0134,0.1690</t>
+  </si>
+  <si>
+    <t>0.5680,0.0005,0.0106,0.2776</t>
+  </si>
+  <si>
+    <t>0.5922,0.0004,0.0145,0.1931</t>
+  </si>
+  <si>
+    <t>0.5869,0.0002,0.0067,0.3320</t>
+  </si>
+  <si>
+    <t>0.4693,0.0049,0.0118,0.3991</t>
+  </si>
+  <si>
+    <t>0.6020,0.0139,0.1181,0.0328</t>
+  </si>
+  <si>
+    <t>0.7589,0.0063,0.0418,0.0677</t>
+  </si>
+  <si>
+    <t>0.5054,0.0005,0.0088,0.4229</t>
+  </si>
+  <si>
+    <t>0.7169,0.0003,0.0038,0.3304</t>
+  </si>
+  <si>
+    <t>0.4672,0.0016,0.0364,0.1667</t>
+  </si>
+  <si>
+    <t>0.7735,0.0007,0.0101,0.1510</t>
+  </si>
+  <si>
+    <t>0.6008,0.0007,0.0093,0.2669</t>
+  </si>
+  <si>
+    <t>0.1758,0.0115,0.6572,0.0098</t>
+  </si>
+  <si>
+    <t>0.5662,0.0020,0.0526,0.0750</t>
   </si>
   <si>
     <t>0.0313,0.0172,0.9515,0.0090</t>
   </si>
   <si>
-    <t>0.0167,0.0903,0.8649,0.0457</t>
-  </si>
-  <si>
-    <t>0.4403,0.0085,0.1294,0.1793</t>
-  </si>
-  <si>
-    <t>0.0090,0.1764,0.9653,0.0029</t>
-  </si>
-  <si>
-    <t>0.0478,0.0158,0.8490,0.0402</t>
-  </si>
-  <si>
-    <t>0.1856,0.0041,0.7858,0.0050</t>
-  </si>
-  <si>
-    <t>0.3500,0.0139,0.5975,0.0090</t>
-  </si>
-  <si>
-    <t>0.6366,0.0189,0.2236,0.0362</t>
-  </si>
-  <si>
-    <t>0.7685,0.0032,0.2351,0.0042</t>
-  </si>
-  <si>
-    <t>0.8074,0.0059,0.0447,0.0556</t>
-  </si>
-  <si>
-    <t>0.6726,0.0097,0.1811,0.0211</t>
-  </si>
-  <si>
-    <t>0.4789,0.0160,0.3330,0.0237</t>
-  </si>
-  <si>
-    <t>0.6014,0.0093,0.4319,0.0038</t>
-  </si>
-  <si>
-    <t>0.5386,0.0131,0.1812,0.0518</t>
-  </si>
-  <si>
-    <t>0.8318,0.0122,0.0954,0.0248</t>
-  </si>
-  <si>
-    <t>0.5234,0.0055,0.0281,0.3418</t>
-  </si>
-  <si>
-    <t>0.7514,0.0019,0.0212,0.0867</t>
+    <t>0.0167,0.0902,0.8650,0.0457</t>
+  </si>
+  <si>
+    <t>0.4402,0.0085,0.1295,0.1792</t>
+  </si>
+  <si>
+    <t>0.0090,0.1762,0.9653,0.0029</t>
+  </si>
+  <si>
+    <t>0.0478,0.0158,0.8490,0.0403</t>
+  </si>
+  <si>
+    <t>0.1856,0.0041,0.7859,0.0050</t>
+  </si>
+  <si>
+    <t>0.3501,0.0139,0.5974,0.0090</t>
+  </si>
+  <si>
+    <t>0.6366,0.0189,0.2237,0.0361</t>
+  </si>
+  <si>
+    <t>0.7686,0.0032,0.2352,0.0042</t>
+  </si>
+  <si>
+    <t>0.8075,0.0059,0.0447,0.0556</t>
+  </si>
+  <si>
+    <t>0.6727,0.0097,0.1812,0.0211</t>
+  </si>
+  <si>
+    <t>0.4789,0.0160,0.3332,0.0237</t>
+  </si>
+  <si>
+    <t>0.6014,0.0093,0.4320,0.0038</t>
+  </si>
+  <si>
+    <t>0.5387,0.0131,0.1813,0.0517</t>
+  </si>
+  <si>
+    <t>0.8319,0.0122,0.0954,0.0248</t>
+  </si>
+  <si>
+    <t>0.5234,0.0055,0.0281,0.3416</t>
+  </si>
+  <si>
+    <t>0.7513,0.0019,0.0212,0.0867</t>
   </si>
   <si>
     <t>0.7080,0.0015,0.0212,0.0986</t>
   </si>
   <si>
-    <t>0.6509,0.0011,0.0105,0.2804</t>
-  </si>
-  <si>
-    <t>0.4972,0.0010,0.0075,0.4582</t>
-  </si>
-  <si>
-    <t>0.8124,0.0101,0.0422,0.0524</t>
+    <t>0.6507,0.0011,0.0105,0.2804</t>
+  </si>
+  <si>
+    <t>0.4970,0.0010,0.0076,0.4583</t>
+  </si>
+  <si>
+    <t>0.8126,0.0101,0.0422,0.0524</t>
   </si>
   <si>
     <t>0.9306,0.0007,0.0090,0.0361</t>
   </si>
   <si>
-    <t>0.6259,0.0068,0.0341,0.2271</t>
-  </si>
-  <si>
-    <t>0.7682,0.0057,0.1958,0.0140</t>
-  </si>
-  <si>
-    <t>0.7563,0.0026,0.0467,0.0661</t>
-  </si>
-  <si>
-    <t>0.1537,0.0220,0.7404,0.0167</t>
-  </si>
-  <si>
-    <t>0.7050,0.0068,0.1114,0.1580</t>
-  </si>
-  <si>
-    <t>0.5081,0.0215,0.1724,0.2143</t>
+    <t>0.6260,0.0068,0.0341,0.2270</t>
+  </si>
+  <si>
+    <t>0.7682,0.0057,0.1959,0.0140</t>
+  </si>
+  <si>
+    <t>0.7563,0.0026,0.0467,0.0660</t>
+  </si>
+  <si>
+    <t>0.1537,0.0220,0.7403,0.0168</t>
+  </si>
+  <si>
+    <t>0.7049,0.0068,0.1115,0.1580</t>
+  </si>
+  <si>
+    <t>0.5082,0.0215,0.1724,0.2142</t>
   </si>
   <si>
     <t>0.0412,0.0125,0.9536,0.0013</t>
   </si>
   <si>
-    <t>0.2155,0.0549,0.6423,0.0197</t>
-  </si>
-  <si>
-    <t>0.4183,0.0003,0.0102,0.4630</t>
-  </si>
-  <si>
-    <t>0.7068,0.0006,0.0140,0.1158</t>
-  </si>
-  <si>
-    <t>0.2218,0.0008,0.0086,0.7468</t>
-  </si>
-  <si>
-    <t>0.6086,0.0003,0.0046,0.4946</t>
-  </si>
-  <si>
-    <t>0.5670,0.0004,0.0091,0.2916</t>
-  </si>
-  <si>
-    <t>0.6168,0.0005,0.0127,0.1973</t>
-  </si>
-  <si>
-    <t>0.5112,0.0007,0.0204,0.2336</t>
-  </si>
-  <si>
-    <t>0.6611,0.0007,0.0298,0.0871</t>
+    <t>0.2154,0.0548,0.6425,0.0196</t>
+  </si>
+  <si>
+    <t>0.4179,0.0003,0.0102,0.4630</t>
+  </si>
+  <si>
+    <t>0.7067,0.0006,0.0140,0.1157</t>
+  </si>
+  <si>
+    <t>0.2218,0.0008,0.0087,0.7467</t>
+  </si>
+  <si>
+    <t>0.6086,0.0003,0.0046,0.4944</t>
+  </si>
+  <si>
+    <t>0.5669,0.0004,0.0091,0.2916</t>
+  </si>
+  <si>
+    <t>0.6166,0.0005,0.0128,0.1972</t>
+  </si>
+  <si>
+    <t>0.5110,0.0007,0.0204,0.2337</t>
+  </si>
+  <si>
+    <t>0.6608,0.0007,0.0299,0.0871</t>
   </si>
   <si>
     <t>0.4649,0.0030,0.1018,0.0926</t>
   </si>
   <si>
-    <t>0.3991,0.0044,0.0826,0.1509</t>
-  </si>
-  <si>
-    <t>0.4643,0.0034,0.0536,0.1879</t>
+    <t>0.3990,0.0044,0.0827,0.1509</t>
+  </si>
+  <si>
+    <t>0.4642,0.0034,0.0536,0.1877</t>
   </si>
   <si>
     <t>0.0067,0.0222,0.9904,0.0006</t>
@@ -1495,13 +1501,13 @@
     <t>0.0019,0.0175,0.9949,0.0010</t>
   </si>
   <si>
-    <t>0.2221,0.0316,0.7042,0.0090</t>
+    <t>0.2222,0.0315,0.7042,0.0090</t>
   </si>
   <si>
     <t>0.0002,0.0042,0.9995,0.0001</t>
   </si>
   <si>
-    <t>0.3101,0.0166,0.6746,0.0026</t>
+    <t>0.3101,0.0166,0.6747,0.0026</t>
   </si>
   <si>
     <t>0.0001,0.0020,0.9999,0.0000</t>
@@ -1510,10 +1516,10 @@
     <t>0.0153,0.0284,0.9802,0.0009</t>
   </si>
   <si>
-    <t>0.5109,0.0266,0.2104,0.0515</t>
-  </si>
-  <si>
-    <t>0.9331,0.0008,0.0199,0.0206</t>
+    <t>0.5111,0.0265,0.2104,0.0514</t>
+  </si>
+  <si>
+    <t>0.9331,0.0008,0.0199,0.0205</t>
   </si>
   <si>
     <t>0.7332,0.0008,0.0147,0.1931</t>
@@ -1522,49 +1528,49 @@
     <t>0.9433,0.0006,0.0058,0.0348</t>
   </si>
   <si>
-    <t>0.4683,0.0004,0.0043,0.6398</t>
-  </si>
-  <si>
-    <t>0.5977,0.0004,0.0049,0.5126</t>
-  </si>
-  <si>
-    <t>0.6636,0.0005,0.0143,0.1463</t>
-  </si>
-  <si>
-    <t>0.4375,0.0019,0.0301,0.2303</t>
-  </si>
-  <si>
-    <t>0.6486,0.0007,0.0093,0.3332</t>
-  </si>
-  <si>
-    <t>0.5204,0.0010,0.0141,0.3105</t>
-  </si>
-  <si>
-    <t>0.3971,0.0003,0.0041,0.6473</t>
-  </si>
-  <si>
-    <t>0.4076,0.0012,0.0130,0.4931</t>
-  </si>
-  <si>
-    <t>0.1299,0.0345,0.8359,0.0023</t>
+    <t>0.4679,0.0004,0.0043,0.6400</t>
+  </si>
+  <si>
+    <t>0.5977,0.0004,0.0049,0.5124</t>
+  </si>
+  <si>
+    <t>0.6635,0.0005,0.0143,0.1463</t>
+  </si>
+  <si>
+    <t>0.4374,0.0019,0.0301,0.2301</t>
+  </si>
+  <si>
+    <t>0.6484,0.0007,0.0093,0.3333</t>
+  </si>
+  <si>
+    <t>0.5203,0.0010,0.0141,0.3104</t>
+  </si>
+  <si>
+    <t>0.3970,0.0003,0.0041,0.6473</t>
+  </si>
+  <si>
+    <t>0.4075,0.0012,0.0130,0.4931</t>
+  </si>
+  <si>
+    <t>0.1299,0.0345,0.8360,0.0023</t>
   </si>
   <si>
     <t>0.0342,0.0407,0.9530,0.0011</t>
   </si>
   <si>
-    <t>0.0152,0.0329,0.9806,0.0007</t>
-  </si>
-  <si>
-    <t>0.2775,0.0196,0.6942,0.0049</t>
+    <t>0.0152,0.0328,0.9806,0.0007</t>
+  </si>
+  <si>
+    <t>0.2777,0.0196,0.6941,0.0049</t>
   </si>
   <si>
     <t>0.4848,0.0056,0.5132,0.0033</t>
   </si>
   <si>
-    <t>0.1944,0.0009,0.0055,0.9410</t>
-  </si>
-  <si>
-    <t>0.5082,0.0032,0.0389,0.4802</t>
+    <t>0.1942,0.0009,0.0055,0.9410</t>
+  </si>
+  <si>
+    <t>0.5081,0.0032,0.0390,0.4801</t>
   </si>
   <si>
     <t>0.0122,0.0279,0.9791,0.0022</t>
@@ -1576,7 +1582,7 @@
     <t>0.3084,0.0004,0.0009,0.8715</t>
   </si>
   <si>
-    <t>0.0637,0.0002,0.0013,0.9843</t>
+    <t>0.0637,0.0002,0.0013,0.9844</t>
   </si>
   <si>
     <t>0.0043,0.0004,0.0039,0.9990</t>
@@ -1971,7 +1977,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1991,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1996,10 +2002,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2010,10 +2016,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2027,7 +2033,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2047,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2061,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2069,7 +2075,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2089,7 @@
         <v>265</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2103,7 @@
         <v>265</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2117,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2131,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2145,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,10 +2156,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2167,7 +2173,7 @@
         <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2181,7 +2187,7 @@
         <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,7 +2201,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,10 +2212,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2223,7 +2229,7 @@
         <v>264</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2237,7 +2243,7 @@
         <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2251,7 +2257,7 @@
         <v>264</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,10 +2268,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,7 +2285,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2293,7 +2299,7 @@
         <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,10 +2310,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2321,7 +2327,7 @@
         <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2335,7 +2341,7 @@
         <v>264</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2349,7 +2355,7 @@
         <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,10 +2366,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2383,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2388,10 +2394,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,10 +2408,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2419,7 +2425,7 @@
         <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2439,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2453,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2461,7 +2467,7 @@
         <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2472,10 +2478,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,10 +2492,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,10 +2506,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,10 +2520,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2531,7 +2537,7 @@
         <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,10 +2548,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,10 +2562,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,10 +2576,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,7 +2593,7 @@
         <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,10 +2604,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,10 +2618,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,10 +2632,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,10 +2646,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,10 +2660,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,10 +2674,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2685,7 +2691,7 @@
         <v>264</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,10 +2702,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,10 +2716,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2727,7 +2733,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2747,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2761,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2766,10 +2772,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2783,7 +2789,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2803,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2811,7 +2817,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,10 +2828,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,10 +2842,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,10 +2856,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,10 +2870,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,10 +2884,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D67" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,10 +2898,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,10 +2912,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D69" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2929,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,10 +2940,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2948,10 +2954,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D72" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,10 +2968,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,10 +2982,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,10 +2996,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D75" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,10 +3010,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3027,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3041,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3055,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3069,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3083,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3091,7 +3097,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,10 +3108,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,10 +3122,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,10 +3136,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,10 +3150,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,10 +3164,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,10 +3178,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3186,10 +3192,10 @@
         <v>259</v>
       </c>
       <c r="C89" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D89" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3200,10 +3206,10 @@
         <v>259</v>
       </c>
       <c r="C90" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D90" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3223,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3237,7 @@
         <v>265</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3251,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3265,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3270,10 +3276,10 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3293,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3307,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3321,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3335,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3349,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3363,7 @@
         <v>265</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3377,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3382,10 +3388,10 @@
         <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3399,7 +3405,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,10 +3416,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,10 +3430,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3447,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3455,7 +3461,7 @@
         <v>264</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,10 +3472,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,10 +3486,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,10 +3500,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3511,7 +3517,7 @@
         <v>264</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,10 +3528,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,10 +3542,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3553,7 +3559,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3567,7 +3573,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3581,7 +3587,7 @@
         <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3601,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3609,7 +3615,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3623,7 +3629,7 @@
         <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,10 +3640,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,10 +3654,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,10 +3668,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,10 +3682,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,10 +3696,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,10 +3710,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3721,7 +3727,7 @@
         <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3741,7 @@
         <v>265</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3755,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3760,10 +3766,10 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3783,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3797,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3802,10 +3808,10 @@
         <v>259</v>
       </c>
       <c r="C133" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3825,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3833,7 +3839,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,10 +3850,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,10 +3864,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,10 +3878,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,10 +3892,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3909,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3917,7 +3923,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3931,7 +3937,7 @@
         <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3945,7 +3951,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3965,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3973,7 +3979,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3987,7 +3993,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4007,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,10 +4018,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4035,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4040,10 +4046,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4057,7 +4063,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4071,7 +4077,7 @@
         <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4091,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4096,10 +4102,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,10 +4116,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,10 +4130,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4141,7 +4147,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4161,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4166,10 +4172,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4189,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4203,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,10 +4214,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4231,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4245,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4253,7 +4259,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4273,7 @@
         <v>265</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4287,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4295,7 +4301,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4315,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4323,7 +4329,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4343,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4357,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,10 +4368,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4379,7 +4385,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4393,7 +4399,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4407,7 +4413,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4421,7 +4427,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4432,10 +4438,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4449,7 +4455,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4469,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4474,10 +4480,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4491,7 +4497,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,10 +4508,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,10 +4522,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,10 +4536,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,10 +4550,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,10 +4564,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,10 +4578,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,10 +4592,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4603,7 +4609,7 @@
         <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4617,7 +4623,7 @@
         <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4637,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4645,7 +4651,7 @@
         <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4656,10 +4662,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4673,7 +4679,7 @@
         <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4687,7 +4693,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4701,7 +4707,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4715,7 +4721,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4729,7 +4735,7 @@
         <v>264</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4743,7 +4749,7 @@
         <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4757,7 +4763,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4768,10 +4774,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4785,7 +4791,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4805,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,7 +4819,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4827,7 +4833,7 @@
         <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4841,7 +4847,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,10 +4858,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4869,7 +4875,7 @@
         <v>264</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4883,7 +4889,7 @@
         <v>264</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,10 +4900,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,10 +4914,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4922,10 +4928,10 @@
         <v>259</v>
       </c>
       <c r="C213" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4945,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4959,7 @@
         <v>265</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4973,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4987,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +5001,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5015,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5023,7 +5029,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,10 +5040,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5048,10 +5054,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5062,10 +5068,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,10 +5082,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,10 +5096,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,10 +5110,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,10 +5124,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,10 +5138,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,10 +5152,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D229" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,10 +5166,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5177,7 +5183,7 @@
         <v>264</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5191,7 +5197,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5205,7 +5211,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5225,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5239,7 @@
         <v>265</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5244,10 +5250,10 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5267,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5272,10 +5278,10 @@
         <v>259</v>
       </c>
       <c r="C238" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5289,7 +5295,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5309,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5323,7 @@
         <v>265</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5328,10 +5334,10 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,10 +5348,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,10 +5362,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,10 +5376,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,10 +5390,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,10 +5404,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5421,7 @@
         <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5429,7 +5435,7 @@
         <v>264</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,10 +5446,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5457,7 +5463,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5477,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5491,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5499,7 +5505,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5513,7 +5519,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5533,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
